--- a/backtest_runs/20260410_193731/by_symbol/IGIL/IGIL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/IGIL/IGIL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
         <v>-3333.120000000003</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>96666.87999999999</v>
@@ -909,7 +909,7 @@
         <v>-10780.56</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>85886.31999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-10103.51999999999</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>84948.88000000002</v>
@@ -1323,7 +1323,7 @@
         <v>-1197.840000000002</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>83751.04000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-8072.400000000003</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>76147.36000000002</v>
@@ -1461,7 +1461,7 @@
         <v>-989.5200000000067</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>75157.84</v>
